--- a/dados.xlsx
+++ b/dados.xlsx
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t xml:space="preserve">Ano</t>
+  </si>
   <si>
     <t xml:space="preserve">Titular</t>
   </si>
@@ -110,8 +113,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -307,95 +314,112 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16380" min="16380" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>149</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>181</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>28</v>
       </c>
     </row>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -10,6 +10,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$C$8</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -20,24 +23,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t xml:space="preserve">Ano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Titular</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t xml:space="preserve">Clube</t>
   </si>
   <si>
     <t xml:space="preserve">Gols</t>
   </si>
   <si>
-    <t xml:space="preserve">Assistencias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finalizações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chutes a gol</t>
+    <t xml:space="preserve">Jogos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sporting B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manchester United</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Madrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juventus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al-Nassr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal</t>
   </si>
 </sst>
 </file>
@@ -118,7 +133,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -131,7 +146,28 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -314,13 +350,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:C1048576"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16380" min="16380" style="0" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -333,97 +366,87 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>129</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>149</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>181</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>72</v>
+      <c r="B4" s="0" t="n">
+        <v>145</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>346</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>28</v>
-      </c>
-    </row>
+      <c r="A5" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>450</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>143</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -431,5 +454,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>